--- a/产权管理领域穿透式监管风险库.xlsx
+++ b/产权管理领域穿透式监管风险库.xlsx
@@ -591,16 +591,16 @@
         <is>
           <t>产权转让事项立项后，承办单位应录入转让方、标的企业、持股比例、评估基准日、拟转让方式、预计交易金额等基础信息，由产权管理部门依据公司章程、授权清单和事项性质确定决策主体、审批层级及必备材料，形成该事项唯一编号和审批路径。
 进入挂牌、协议签署或交割前，应分别校验党委前置研究、董事会或股东会决议、上级批复等文件是否齐备、有效且与当前交易方案一致。发生标的、比例、底价、转让方式、受让条件等实质变化的，应重新判断是否需要补充论证或重新履行决策，不得沿用失效或不匹配的批复。
-未取得有效批复不得发布挂牌公告、签署具有约束力的协议、收取交易价款或移交控制权。系统发现批复日晚于挂牌、签约或交割日期时，应暂停后续流程并生成异常事项；责任单位说明原因、完成合规复核和整改，经产权管理部门确认后方可关闭，处理过程全程留痕。</t>
+未取得有效批复不得发布挂牌公告、签署具有约束力的协议、收取交易价款或移交控制权。产权管理部门审核发现批复日晚于挂牌、签约或交割日期时，应暂停后续流程，要求责任单位说明原因并提交整改材料；经复核确认审批文件有效、交易要素一致且整改责任落实后方可继续，审核意见和处理依据应完整归档。</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>指标名称：未批先行产权转让事项数
-指标定义：反映产权转让事项在有效决策审批完成前已进入挂牌、签约或交割环节的情况。
-指标计算：未批先行产权转让事项数＝报告期内批复生效日晚于首次交易实施日或无有效批复的事项数量
-其中，批复生效日取最终有权审批主体批复生效日期；首次交易实施日取挂牌公告日、具有约束力协议签署日、价款收取日或控制权移交日中的最早日期。
-监控规则：系统持续比对审批和交易时点，发现倒序或无有效批复的事项即形成预警，推送产权管理部门核实；经确认属于未批先行的，暂停后续流程并纳入整改跟踪，复核通过后关闭。</t>
+          <t>指标名称：未批先行交易金额占比
+指标定义：反映未经有效决策审批即进入实质实施环节的产权转让金额在全部产权转让金额中的比重，用于衡量决策审批约束的有效性及未授权国有权益暴露程度。
+指标计算：未批先行交易金额占比＝未批先行产权转让实际对价÷报告期产权转让实际对价总额×100%
+其中，未批先行是指批复生效日晚于首次交易实施日或无有效批复；首次交易实施日取挂牌公告、约束性协议签署、价款收取或控制权移交的最早日期。报告期无产权转让时不计算比例。
+监控规则：按产权转让事项持续监测，重点关注指标新增、上升及涉及重大国有权益的单项交易；发现未批先行后立即暂停未完成环节，核实决策效力和权益影响，完成整改及责任处理后闭环。</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -689,17 +689,17 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>产权管理部门应将现行授权文件转化为结构化授权清单，至少明确被授权主体、事项类型、金额口径、适用范围、生效及失效日期、禁止事项和需升级审批的例外情形，并由授权管理责任部门定期确认版本有效性。
-转让申请提交时，承办单位应完整录入评估值、拟定底价、预计成交金额、标的类型和交易方式。系统按有效授权版本匹配审批层级；存在多项判断口径的，从严确定权限。交易方案发生金额、比例、方式或标的范围变化时，应重新执行权限判断，不得以初始判断代替变更后的审批。
+转让申请提交时，承办单位应完整说明评估值、拟定底价、预计成交金额、标的类型和交易方式。产权管理部门应依据交易实施时有效的授权文件逐项判断审批层级；存在金额口径交叉、事项性质难以确定或多个授权条款同时适用的，从严确定权限并形成书面判断意见。交易方案发生金额、比例、方式或标的范围变化时，应重新执行权限判断，不得以初始判断代替变更后的审批。
 超出本级授权或无法匹配有效授权的事项，应自动转入上级审批，不得由本级决策后继续挂牌、签约或交割。发现已实施的越权事项，应立即登记异常、保存交易证据、评估法律效力和国有权益影响，形成整改及责任处理意见并闭环跟踪。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>指标名称：超越授权范围实施的产权转让事项数
-指标定义：反映产权转让实际审批层级低于有效授权规则要求的情况。
-指标计算：超越授权事项数＝报告期内实际审批层级低于规则匹配审批层级的事项数量
-其中，规则匹配审批层级依据交易实施时有效的授权版本及事项类型、金额口径、标的性质等要素计算；实际审批层级取最终批复主体。
-监控规则：系统在申请及方案变更时重新匹配权限，出现审批层级不足、授权失效或事项超出授权范围时预警并阻断；核实后转上级审批，已实施事项纳入专项整改。</t>
+          <t>指标名称：越权产权转让金额占比
+指标定义：反映实际审批层级低于有效授权规则要求的产权转让金额占比，用于评价各级企业授权执行质量和越权处置国有权益的风险暴露。
+指标计算：越权产权转让金额占比＝经核实超越授权范围的产权转让实际对价÷报告期产权转让实际对价总额×100%
+其中，授权范围按照交易实施时有效的授权文件，结合事项类型、金额口径、标的性质和交易方式判定；报告期无产权转让时不计算比例。
+监控规则：按法人主体和授权层级监测指标变化，出现越权交易即复核授权版本和审批路径；未实施事项升级履行审批，已实施事项开展法律效力、权益影响和责任认定专项处置。</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>承办单位在立项时应披露同一标的、同类资产、同一受让方及其关联方已经实施或计划实施的相关交易，并说明各交易是否属于同一整体处置方案。产权管理部门应基于交易目的、资产功能关联、决策形成过程和受让方关系判断是否应合并管理。
-系统对相近期间内同一转让方或同一控制链条主体实施的交易进行聚合，重点识别同一标的股权分批转让、成套资产拆分、向同一或关联受让方连续转让、单笔均低于审批或进场标准但累计达到相关标准等组合。命中规则仅作为疑似线索，不直接认定违规。
+产权管理部门审核时应汇总相近期间内同一转让方或同一控制链条主体实施的交易，重点识别同一标的股权分批转让、成套资产拆分、向同一或关联受让方连续转让、单笔均低于审批或进场标准但累计达到相关标准等组合。仅有时间接近不得直接认定拆分，还应结合交易目的、标的关联性、决策过程和受让方关系作实质判断。
 疑似组合应由产权、法律、财务等部门联合复核。认定属于同一经济行为的，应按合并后的交易规模重新确定决策审批、审计评估和进场交易要求；未完成相应程序前暂停后续交易，并记录判断依据、整改措施及复核结论。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>指标名称：疑似拆分规避产权转让组合数
-指标定义：反映相近期间内具有相同标的、受让方关联或资产功能关联，单笔未达到监管标准但聚合后达到相应标准的交易组合。
-指标计算：疑似组合数＝按转让主体、标的或资产类别、受让方关联关系和观察周期聚合后命中拆分识别规则的组合数量
-其中，观察周期和聚合口径由授权及交易管理规则配置；关联受让方依据统一社会信用代码、股权关系、实际控制人等信息识别。
-监控规则：系统滚动聚合并形成疑似组合清单，推送产权管理部门进行实质判断；确认属于同一经济行为的，暂停交易并按合并口径补充履行程序，排除的应记录理由。</t>
+          <t>指标名称：应合并管理交易金额占比
+指标定义：反映经实质复核属于同一经济行为、应合并履行审批或进场程序的交易金额占全部产权转让金额的比重，用于识别拆分交易对监管有效性的影响。
+指标计算：应合并管理交易金额占比＝经复核认定应合并管理的关联交易累计实际对价÷报告期产权转让实际对价总额×100%
+其中，关联交易按转让主体、标的或资产功能、受让方关联关系和管理观察周期归集；仅规则命中但尚未完成实质复核的交易不计入分子，单独列为待核查线索。
+监控规则：定期汇总待核查组合和经确认金额，关注指标变化及重复发生主体；确认应合并管理的，按合并口径重新履行决策、评估和交易程序，并分析拆分形成原因。</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>指标名称：审计评估及备案程序异常事项数
-指标定义：反映应履行审计评估或核准备案程序但在交易启动前未完成，或者所用报告与交易事项不匹配、已失效的情况。
-指标计算：程序异常事项数＝应审未审事项数＋应评未评事项数＋未完成核准备案即交易事项数＋使用无效或不匹配报告事项数
-其中，是否应审应评依据事项类型和制度规则判断；交易启动日取底价确定、挂牌公告或协议签署的最早日期；有效性按备案状态、报告期限及交易要素一致性判断。
-监控规则：系统在立项、定价、挂牌和签约节点校验程序状态，发现缺失、倒序、失效或不匹配即预警并阻断；依法可豁免的，须关联有效依据并经人工复核后放行。</t>
+          <t>指标名称：交易前审计评估备案程序完成率
+指标定义：反映应履行审计、评估及核准备案程序的产权交易，在确定底价或启动交易前完成全部适用程序的比例，用于评价交易定价基础和程序控制质量。
+指标计算：交易前审计评估备案程序完成率＝交易启动前已完成全部适用程序的事项数÷报告期应履行相关程序的产权交易事项总数×100%
+其中，是否应履行相关程序依据事项类型和制度规定判定；依法豁免且已取得有效依据的视为完成；报告期无适用事项时不计算比例。
+监控规则：按事项类型和责任单位定期分析完成率及未完成原因；任何未完成适用程序即启动交易的事项均应暂停后续实施，补充专业复核或重新履行程序后方可继续。</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,11 +1026,11 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>指标名称：产权交易价格偏离事项数
-指标定义：反映产权交易成交价或调整后的实际对价低于备案评估值或经批准定价依据的情况。
-指标计算：价格偏离事项数＝报告期内实际对价低于适用定价基准且未关联有效批准或充分说明的事项数量
-其中，实际对价为成交价扣减债权豁免、费用代担及其他由转让方承担的经济利益后的金额；适用定价基准依据备案评估值及经批准的定价规则确定。
-监控规则：系统计算价格偏离并核验批准依据，出现未说明偏离或附带安排降低对价时预警，推送产权、财务和法律部门复核；确认影响国有权益的，暂停签约或交割并重新履行审批。</t>
+          <t>指标名称：产权交易实际对价基准偏离率
+指标定义：反映交易实际取得的经济利益相对经批准定价基准的向下偏离程度，用于评价定价公允性及国有权益让渡风险。
+指标计算：产权交易实际对价基准偏离率＝（经批准定价基准－调整后实际对价）÷经批准定价基准×100%
+其中，调整后实际对价为成交价扣减债权豁免、费用代担、收益让渡等由转让方承担的经济利益；指标按单项交易计算，正值表示实际对价低于基准，经批准定价基准为零时不计算。
+监控规则：逐项监测向下偏离及其形成原因，区分公开竞价结果、经批准价格调整和未经批准权益让渡；未经充分论证和有效批准的向下偏离，应暂停签约或交割并重新审查定价及附带安排。</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>产权事项立项时应依据标的类型、交易方式和制度规定形成进场交易判断。拟采取非公开协议方式的，应说明适用条件并取得有权主体批准；不符合豁免条件的，不得以内部协议、长期租赁或其他安排替代进场交易。
-进场事项应通过规定的产权交易机构公开披露。挂牌申请须包含标的基本情况、审计评估结果、转让底价、受让方条件、重大债权债务和职工安置等应披露内容。系统按交易类型校验规定披露期间；挂牌条件或重要信息发生实质变更时，应履行重新审批并按规定重新披露。
+进场事项应通过规定的产权交易机构公开披露。挂牌申请须包含标的基本情况、审计评估结果、转让底价、受让方条件、重大债权债务和职工安置等应披露内容。承办人员应依据交易类型填写信息披露要件清单，复核人员逐项核对披露期间、披露内容与批准方案的一致性；挂牌条件或重要信息发生实质变更时，应履行重新审批并按规定重新披露。
 竞价及成交后，应取得交易机构出具的挂牌、竞价和成交凭证，并与内部批准的标的、底价、受让条件和成交结果核对。未进场、披露期不足、披露内容缺失或擅自变更条件的事项，应暂停竞价、签约或交割，完成纠正后方可继续。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>指标名称：进场及信息披露程序异常事项数
-指标定义：反映应进场交易事项无交易机构有效记录，或信息披露期间、内容及变更程序不符合适用规则的情况。
-指标计算：程序异常事项数＝应进场无有效挂牌成交记录事项数＋披露期间不符合规定事项数＋关键披露字段缺失或未经程序变更事项数
-其中，应进场范围和披露要求依据事项类型及有效制度规则确定；有效记录由内部事项编号与交易机构项目编号匹配确认。
-监控规则：系统持续比对内部事项与交易机构记录，发现无匹配记录、披露期间不足、关键字段缺失或条件异常变更时预警并阻断后续节点；人工复核确认后要求重新进场或补充披露。</t>
+          <t>指标名称：进场及信息披露程序合规率
+指标定义：反映应公开交易事项完整履行进场、信息披露和条件变更程序的比例，用于评价产权交易公开、公平和可追溯程度。
+指标计算：进场及信息披露程序合规率＝完整履行适用进场及披露程序的事项数÷报告期应进场交易事项总数×100%
+其中，完整履行是指具有有效交易机构记录，披露期间符合规定，关键内容完整，挂牌条件变更已履行相应审批和披露程序；依法协议转让且批准依据有效的事项不纳入分母。
+监控规则：按交易类型和所属单位分析合规率及缺陷类型；未进场、披露不完整或擅自改变交易条件的事项不得继续签约交割，应重新进场、补充披露或履行变更程序。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1217,18 +1217,18 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>总部应建立以统一社会信用代码为主键的法人主数据，明确产权登记、工商登记、财务决算和投资管理系统的字段口径、更新责任和同步时点。新增、变动、注销事项完成后，各责任系统应按同一经济行为及时更新。
-系统定期比对企业名称、登记状态、直接及间接股东、持股比例、控制关系、产权级次和财务并表状态。对因时间差产生的暂时差异，应关联在途变更事项和预计完成日期；对无法由在途事项解释的差异，自动分派至产权、财务或投资管理责任单位。
-责任单位应依据工商档案、出资凭证、公司章程、股东名册和批准文件核实真实持股关系，明确应更正的数据源和完成时限。涉及并表范围判断的，由财务部门形成专业结论；涉及产权登记错误的，完成登记变更后回传凭证，系统复核一致后关闭。</t>
+          <t>总部应建立以统一社会信用代码为主键的法人主数据标准，明确产权登记、工商登记、财务决算和投资管理台账的字段口径、资料责任和信息更新时间。新增、变动、注销事项完成后，各责任部门应依据同一经济行为凭证及时更新所负责的信息。
+产权、财务和投资管理部门应定期联合比对企业名称、登记状态、直接及间接股东、持股比例、控制关系、产权级次和财务并表状态。比对结果应区分在途变更、口径差异和实质错误；因时间差形成的暂时差异须关联批准文件、在途事项和预计完成日期，无法解释的差异按字段责任移交相应归口部门核实。
+责任单位应依据工商档案、出资凭证、公司章程、股东名册和批准文件核实真实持股关系，明确应更正的数据源和完成时限。涉及并表范围判断的，由财务部门形成书面专业结论；涉及产权登记错误的，应完成登记变更并提交凭证。各归口部门交叉复核关键字段一致后方可关闭差异。</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>指标名称：产权多源数据不一致企业数
-指标定义：反映产权登记、工商登记、财务并表范围及实际持股台账之间关键字段存在无法由在途事项解释的差异。
-指标计算：不一致企业数＝关键字段比对不一致且未关联有效在途变更事项的企业去重数量
-其中，关键字段包括企业状态、股东名称、持股比例、控制关系、产权级次和并表状态；同一企业存在多项差异按一家统计并保留差异明细。
-监控规则：系统定期执行全量及增量比对，发现差异后按数据责任分派核实；在途差异持续跟踪，超过计划完成日期仍未消除时升级预警，完成源系统更正并复核一致后关闭。</t>
+          <t>指标名称：产权关键数据一致率
+指标定义：反映产权登记、工商登记、财务并表范围和实际持股台账中法人关键产权信息保持一致的程度，用于评价产权底数质量和并表管理准确性。
+指标计算：产权关键数据一致率＝关键字段全部一致或差异已由有效在途事项解释的企业数÷纳入多源比对的企业总数×100%
+其中，关键字段包括企业状态、股东名称、持股比例、控制关系、产权级次和并表状态；同一企业任一关键字段存在未解释差异即视为不一致。
+监控规则：定期分析总体一致率、差异类型和差异存续时间；对无法由在途事项解释或长期未消除的差异，明确责任数据源并核实真实产权关系，完成登记、工商或财务数据更正后闭环。</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1309,11 +1309,11 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>指标名称：控股企业治理权配置异常数
-指标定义：反映国有股东名义控股，但董事会席位、关键人员任免或重大事项表决安排与控制权要求不匹配的企业数量。
-指标计算：治理权配置异常数＝持股及控制关系满足控股条件但命中治理权异常规则的企业去重数量
-其中，异常规则包括董事席位不足、关键岗位应派未派、重大事项否决或表决权安排削弱控制、章程与实际履职不一致等，具体规则依治理要求配置。
-监控规则：系统定期比对持股关系、章程结构化条款和治理人员数据，命中规则时提示开展实质控制评价；确认控股不控权的纳入治理整改，无法自动判断的转人工复核。</t>
+          <t>指标名称：控股企业关键治理权落实率
+指标定义：反映国有控股企业按照批准方案和章程落实董事席位、关键人员任免、重大事项表决及财务管控等控制权安排的程度，用于评价名义控股向实际控制转化的质量。
+指标计算：控股企业关键治理权落实率＝已实际落实的关键治理权项目数÷应落实的关键治理权项目总数×100%
+其中，应落实项目依据投资方案、章程和公司治理要求确定；仅有条款约定但未完成派员、授权或实际执行的，不计入已落实项目。
+监控规则：按控股企业定期评价落实率，并重点核查关键治理权缺失、长期空缺或无法实际行使的原因；影响实际控制的，应制定章程修订、人员调整、股权优化或退出方案。</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1389,17 +1389,17 @@
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>新设、并购、重组或调整持股路径前，承办单位应提交交易前后股权结构图，说明每一中间持股主体的商业目的、管理职责、税务法律依据和退出安排。产权管理部门应判断新增层级是否符合层级管控要求，能否通过直接持股或简化架构实现同一目的。
-系统基于产权登记和工商数据构建全级次股权树，识别最长持股路径、多个中间载体、循环持股、交叉持股及同一控制链条重复设立主体等情形。境外特殊目的公司或合伙企业资料不完整时，应由责任单位补充股东名册、章程及最终受益所有人信息。
+总部应基于产权登记、工商档案和投资台账绘制全级次股权结构图，逐条识别最长持股路径、多个中间载体、循环持股、交叉持股及同一控制链条重复设立主体等情形。境外特殊目的公司或合伙企业资料不完整时，应由责任单位补充股东名册、章程及最终受益所有人信息，未能说明最终控制关系的不得认定审核材料完整。
 拟新增不必要层级或形成复杂嵌套的事项，应在实施前调整方案或取得专项批准。存量超层级企业应逐户明确保留理由、压缩方式、责任单位和计划节点；涉及注销、划转或吸收合并的，依法履行相应程序并更新产权数据。</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>指标名称：股权层级及嵌套架构异常企业数
-指标定义：反映股权路径超过公司层级管控要求，或存在循环持股、重复中间载体等复杂嵌套情形的企业数量。
-指标计算：架构异常企业数＝命中超层级规则或复杂嵌套识别规则的企业去重数量
-其中，持股层级从集团总部起沿控制链条计算；复杂嵌套依据循环路径、中间载体数量、重复控制链条及专项批准情况识别。
-监控规则：系统在新设和股权变动审批前模拟交易后架构，并定期对存量架构重算；命中规则的提示说明商业必要性或调整方案，未经批准不得新增，存量事项纳入压缩计划跟踪。</t>
+          <t>指标名称：超层级及复杂嵌套企业占比
+指标定义：反映超过公司产权层级管理要求或存在无充分商业必要性复杂嵌套的企业占纳入监测企业的比重，用于评价产权架构精简程度和管理链条复杂性。
+指标计算：超层级及复杂嵌套企业占比＝经核实超出层级要求或存在复杂嵌套的企业数÷纳入产权层级监测的企业总数×100%
+其中，产权层级从集团总部沿控制链条计算；依法设立且具有充分商业必要性并取得专项批准的特殊架构单独列示，不作为未整改异常纳入分子。
+监控规则：定期分析占比变化、新增异常架构和存量压降进展；新增架构应在实施前论证必要性，存量异常逐户制定压缩或规范计划并跟踪完成质量。</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1514,11 +1514,11 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>指标名称：无偿划转及境外处置程序异常事项数
-指标定义：反映已启动实施但未关联适用专项批复，或批复内容与实际处置要素不一致的事项。
-指标计算：程序异常事项数＝事项核查中无有效专项批复或实际实施要素与批复不一致的事项数量
-其中，实施要素包括处置主体、标的、股权比例、交易方式及批复明确的前置条件。
-监控规则：系统在事项关键节点执行要件校验并形成事项预警，不进行高频趋势预警；责任部门补充批复或调整方案，经专项复核后关闭。</t>
+          <t>指标名称：专项审批前置完成率
+指标定义：反映无偿划转及境外产权处置事项在签署生效协议或移交控制权前完成全部适用专项审批和前置条件的比例，用于评价低频重大事项的程序质量。
+指标计算：专项审批前置完成率＝实施前已完成全部专项审批及前置条件的事项数÷报告期无偿划转及境外产权处置事项总数×100%
+其中，专项审批和前置条件依据事项类型、境内外适用规定及批复要求确定；事项方案发生实质变化后未经重新确认的，不视为完整完成。
+监控规则：按事项逐笔监测并在年度汇总分析完成质量；程序未完成或实施要素与批复不一致的，应停止后续实施，补充审批或调整方案并经专项复核。</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>指标名称：评估范围差异事项数
-指标定义：反映产权事项评估申报范围与基准日财务账、资产台账或权属清单存在未解释差异的情况。
-指标计算：评估范围差异事项数＝专项比对中存在未解释资产遗漏或金额差异的产权事项数量
-其中，差异按资产类别、数量、账面金额及评估申报状态列示；已形成合理书面说明并经复核的差异不计入。
-监控规则：系统在评估事项中执行范围勾稽并输出差异清单，推送专业部门按事项复核；确认漏评的暂停备案或交易并补充评估，完成后复核关闭。</t>
+          <t>指标名称：评估范围未覆盖资产金额占比
+指标定义：反映评估申报范围未覆盖且无法合理解释的资产账面金额占基准日应评资产金额的比重，用于评价资产清查和评估范围完整性。
+指标计算：评估范围未覆盖资产金额占比＝经核实未纳入评估范围的应评资产账面金额÷评估基准日应纳入评估范围资产账面金额×100%
+其中，应评资产包括与交易标的相关的账内外资产及可辨认无形资产；已依法排除并形成书面依据的资产不计入分子，无法可靠取得账面金额的项目单独列示。
+监控规则：按评估事项开展范围勾稽，重点关注未覆盖金额、资产类别及形成原因；确认漏评的暂停备案和定价，补充清查评估并复核范围完整性。</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>交易协议应明确交割条件、权属变更资料、双方配合义务、办理责任人、计划完成日期及逾期责任。签约后由承办单位建立交割清单，逐项列示价款支付、资料移交、工商变更、产权登记及专项资产过户状态。
-达到交割条件时，系统自动触发权属变更任务。责任单位应及时取得工商受理、产权登记或其他权属机构凭证；因诉讼保全、抵质押、资料缺失或受让方不配合无法办理的，应说明障碍、责任主体和解决方案，不得仅以“办理中”长期挂账。
+达到交割条件时，承办单位应按照交割清单逐项发起权属变更，及时取得工商受理、产权登记或其他权属机构凭证；复核人员应核对申请主体、标的范围和变更结果与交易协议一致。因诉讼保全、抵质押、资料缺失或受让方不配合无法办理的，应说明障碍、责任主体和解决方案，不得仅以“办理中”长期挂账。
 产权管理部门定期核对交割清单与外部登记状态，对超过计划日期未完成的事项分级督办。涉及国有权益可能受损的，应采取保全、追偿或暂停剩余交割等措施；全部权属更新并复核一致后方可办结事项。</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>指标名称：交割后权属变更未办结事项数
-指标定义：反映产权交易已达到交割条件，但工商、产权登记或相关资产权属变更尚未完成的事项。
-指标计算：未办结事项数＝已完成交割且至少一项应办权属变更状态为未完成的事项数量
-其中，应办权属类型依据交易标的确定；计划完成日期取经审批的交割清单节点，外部登记状态以受理或办结凭证核验。
-监控规则：系统按事项计划节点提醒并对逾期未办结事项预警，推送责任单位说明障碍和更新计划；总部重点跟踪长期未办结及可能影响权益的事项。</t>
+          <t>指标名称：交割后权属变更按期完成率
+指标定义：反映产权交易交割后，各项工商、产权登记及专项资产权属变更在批准计划期限内完成的比例，用于评价交割闭环和权利固化质量。
+指标计算：交割后权属变更按期完成率＝在计划期限内完成全部应办权属变更的事项数÷报告期应办理权属变更的已交割事项总数×100%
+其中，应办权属类型和计划期限依据批准的交割清单确定；因外部法定程序调整且已获批准变更计划的，按调整后计划评价。
+监控规则：按事项跟踪完成率和未办结原因，重点关注长期未完成及可能导致权利悬空的事项；责任单位应提出障碍解决、权益保全和更新计划，全部权属核验一致后办结。</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,16 +1812,16 @@
         <is>
           <t>经济行为获批时，承办单位应根据新设或取得产权、名称股东比例变化、改制合并分立、清算注销或全部产权退出等情形，判断应办理占有、变动或注销登记，并将登记任务纳入经济行为实施方案。
 经济行为完成后，应按制度规定准备批准文件、工商资料、章程、验资或出资证明、审计评估备案和交易凭证，提交产权登记申请。产权管理部门应审核登记类型、产权级次、股东及持股比例、经济行为日期和材料一致性，退回事项应一次性说明补正内容。
-系统跟踪待申报、审核、退回补正、已受理和已办结状态。超过规定办理期限或工商状态已变化但未发起产权登记的，形成专项清理任务；责任单位完成补登、更正并上传登记凭证后，由系统复核经济行为与登记结果一致性。</t>
+产权管理部门应建立登记办理台账，逐项记录待申报、审核、退回补正、已受理和已办结状态。超过规定办理期限或工商状态已变化但未发起产权登记的，应列入专项清理；责任单位完成补登、更正并提交登记凭证后，由经办与复核人员核对经济行为、工商结果和产权登记结果一致性。</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>指标名称：产权登记逾期未办结事项数
-指标定义：反映占有、变动或注销登记触发条件已经成立，但未在制度规定期限内办结的事项。
-指标计算：逾期未办结事项数＝当前日期超过法定或制度办理截止日且登记状态未办结的事项数量
-其中，办理截止日依据经济行为完成日、登记类型及适用规定计算；登记状态以产权登记系统办结结果为准。
-监控规则：系统由经济行为自动生成登记任务并监测期限，临近截止日提醒、超过截止日预警；退回补正和外部原因应记录并持续跟踪，办结后核验结果关闭。</t>
+          <t>指标名称：产权登记按期完成率
+指标定义：反映占有、变动和注销登记在适用规定期限内办结的比例，用于评价产权登记及时性和产权底数更新效率。
+指标计算：产权登记按期完成率＝在规定期限内办结的产权登记事项数÷报告期应办结产权登记事项总数×100%
+其中，办理期限依据经济行为完成日、登记类型及适用规定计算；退回补正不自动中止期限，确有外部原因且已履行延期审批的按批准计划评价。
+监控规则：按登记类型、责任单位和办理环节分析完成率及延误原因；对未按期办结事项逐项补正，核验登记结果与经济行为、工商信息一致后关闭。</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1904,11 +1904,11 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>指标名称：退出企业清理未完成事项数
-指标定义：反映企业退出后，约定应清理的字号、标识、无形资产、域名账号或证照仍存在未完成项目的情况。
-指标计算：清理未完成事项数＝退出清理清单中至少一项任务超过计划完成日期仍未办结的退出企业数量
-其中，退出日期、应清理项目和计划完成日期以经审批的退出方案及交易协议为准；办结需有工商、许可终止、移交销毁等证明。
-监控规则：系统按退出事项跟踪清理清单，未按计划完成时预警并推送责任部门；发现仍对外使用集团身份的升级为专项处置，全部清理并复核后关闭。</t>
+          <t>指标名称：退出清理按期完成率
+指标定义：反映退出企业按照批准方案及时完成字号、标识、无形资产、域名账号和证照清理的比例，用于评价退出风险隔离和品牌权益保护效果。
+指标计算：退出清理按期完成率＝计划期限内完成全部清理项目的退出企业数÷报告期应完成清理的退出企业总数×100%
+其中，应清理项目和计划期限以退出方案及交易协议为准；完成状态须有名称变更、许可终止、移交销毁等有效证明，部分完成不计入分子。
+监控规则：按退出企业跟踪完成率、未清理项目和存续时间；仍对外使用集团身份或无形资产的应优先处置，必要时采取合同追责和法律措施，全部复核通过后办结。</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>指标名称：资质使用主体异常项目数
-指标定义：反映项目合同主体或实际实施主体与资质持有主体不一致，且无合规内部协同依据的疑似项目数量。
-指标计算：主体异常项目数＝命中合同主体、项目人员、资源投入或资金结算主体不一致规则的项目数量
-其中，规则命中仅作为疑似线索；合规内部协同项目须关联有效协议、审批和实质管理证据后排除。
-监控规则：系统按项目进行事项监测，发现多项主体不一致特征时生成核查任务；经专项核查确认出借的立即停止资质使用并整改，排除的记录证据和结论。</t>
+          <t>指标名称：资质使用主体一致率
+指标定义：反映使用企业资质的项目中，合同签约、项目实施、关键人员、资源投入和财务核算主体与资质持有主体保持一致的比例，用于评价资质实质管控能力。
+指标计算：资质使用主体一致率＝经核验主体一致或具有合规内部协同依据的项目数÷报告期使用相关资质的项目总数×100%
+其中，合规内部协同须具备有效协议、审批依据且资质持有企业实际承担项目管理和法律责任；仅名义签约或收取管理费不视为一致。
+监控规则：按资质类型和项目定期抽查一致率，重点核查人员、资金和资源投入分离的项目；确认违规出借或变相使用的，应立即停止、收回授权并处置合同和现场风险。</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2239,14 +2239,14 @@
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>合资前应核查合作方主体资格、信用、资金来源和履约能力，章程及合资协议应明确各方认缴金额、出资方式、分期节点、验资或权属交割要求、逾期责任以及一方未出资时我方暂停后续出资和调整合作方案的权利。
-每个出资节点到期后，财务和产权管理部门应核对银行到账、验资资料或非货币资产权属转移情况。非货币出资应完成评估、权属变更和可使用状态核验；不得仅凭合作方承诺或内部记账认定实缴。出资计划经批准调整的，应同步更新章程、协议和系统计划。
+每个出资节点到期后，财务和产权管理部门应核对银行到账、验资资料或非货币资产权属转移情况。非货币出资应完成评估、权属变更和可使用状态核验；不得仅凭合作方承诺或内部记账认定实缴。出资计划经批准调整的，应同步修订章程、协议和出资计划台账，确保各文件的金额、方式和日期一致。
 合作方未按约出资时，应立即暂停我方后续对等出资和新增资源投入，发出催缴及违约通知，评估稀释股权、解除合作或追偿等措施。定期专项清查抽逃出资、循环验资及我方实际承担全部资金等虚假合资风险，处置完成后复核关闭。</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
           <t>不涉及持续KRI。
-事项监测关注：合作方约定出资节点到期后的未实缴金额、未完成权属转移的非货币出资，以及实缴后短期异常转出的线索。系统按合资协议节点提醒和形成清查名单，是否违约依据有效协议及批准的调整安排核实。</t>
+事项监测关注：合作方约定出资节点到期后的未实缴金额、未完成权属转移的非货币出资，以及实缴后短期异常转出的线索。按合资协议约定的出资节点形成清查名单，是否违约应依据有效协议、到账及权属凭证和经批准的调整安排核实。</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">

--- a/产权管理领域穿透式监管风险库.xlsx
+++ b/产权管理领域穿透式监管风险库.xlsx
@@ -596,11 +596,11 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>指标名称：未批先行交易金额占比
-指标定义：反映未经有效决策审批即进入实质实施环节的产权转让金额在全部产权转让金额中的比重，用于衡量决策审批约束的有效性及未授权国有权益暴露程度。
-指标计算：未批先行交易金额占比＝未批先行产权转让实际对价÷报告期产权转让实际对价总额×100%
-其中，未批先行是指批复生效日晚于首次交易实施日或无有效批复；首次交易实施日取挂牌公告、约束性协议签署、价款收取或控制权移交的最早日期。报告期无产权转让时不计算比例。
-监控规则：按产权转让事项持续监测，重点关注指标新增、上升及涉及重大国有权益的单项交易；发现未批先行后立即暂停未完成环节，核实决策效力和权益影响，完成整改及责任处理后闭环。</t>
+          <t>指标名称：未批先行国有权益暴露金额
+指标定义：反映未取得有效决策审批即进入挂牌、签约、收款或控制权移交环节的产权转让涉及金额，用于监测未经授权处置国有权益的风险规模。
+指标计算：未批先行国有权益暴露金额＝报告期内未批先行产权转让事项实际对价合计
+其中，未批先行是指批复生效日晚于首次交易实施日或无有效批复；首次实施日取挂牌公告、约束性协议签署、价款收取或控制权移交的最早日期。
+监控规则：按月监测当期新增金额和期末未化解金额，并与上期比较变化。出现新增暴露、金额持续增加或涉及重要产权标的时，立即核实交易状态，暂停未完成环节并开展权益影响评估。</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -695,11 +695,11 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>指标名称：越权产权转让金额占比
-指标定义：反映实际审批层级低于有效授权规则要求的产权转让金额占比，用于评价各级企业授权执行质量和越权处置国有权益的风险暴露。
-指标计算：越权产权转让金额占比＝经核实超越授权范围的产权转让实际对价÷报告期产权转让实际对价总额×100%
-其中，授权范围按照交易实施时有效的授权文件，结合事项类型、金额口径、标的性质和交易方式判定；报告期无产权转让时不计算比例。
-监控规则：按法人主体和授权层级监测指标变化，出现越权交易即复核授权版本和审批路径；未实施事项升级履行审批，已实施事项开展法律效力、权益影响和责任认定专项处置。</t>
+          <t>指标名称：越权产权转让金额
+指标定义：反映实际审批层级低于有效授权规则要求的产权转让金额，用于监测各级企业超越授权处置国有权益的风险规模。
+指标计算：越权产权转让金额＝报告期内经核实超越授权范围实施的产权转让实际对价合计
+其中，授权范围按照交易实施时有效的授权文件，结合事项类型、金额口径、标的性质和交易方式判定；尚在核实的事项单独列示为疑似金额。
+监控规则：按月监测疑似金额、确认金额及整改后未化解金额，关注新增越权主体和重复发生单位。确认越权后，应评价交易效力和国有权益影响，升级审批或实施专项整改。</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -778,11 +778,11 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>指标名称：应合并管理交易金额占比
-指标定义：反映经实质复核属于同一经济行为、应合并履行审批或进场程序的交易金额占全部产权转让金额的比重，用于识别拆分交易对监管有效性的影响。
-指标计算：应合并管理交易金额占比＝经复核认定应合并管理的关联交易累计实际对价÷报告期产权转让实际对价总额×100%
-其中，关联交易按转让主体、标的或资产功能、受让方关联关系和管理观察周期归集；仅规则命中但尚未完成实质复核的交易不计入分子，单独列为待核查线索。
-监控规则：定期汇总待核查组合和经确认金额，关注指标变化及重复发生主体；确认应合并管理的，按合并口径重新履行决策、评估和交易程序，并分析拆分形成原因。</t>
+          <t>指标名称：疑似拆分规避交易累计金额
+指标定义：反映相近期间内具有同一标的、资产功能关联或受让方关联关系，可能通过拆分规避审批、评估或进场程序的交易规模。
+指标计算：疑似拆分规避交易累计金额＝命中拆分识别条件的关联交易组合实际对价合计
+其中，交易组合按转让主体、标的或资产类别、受让方关联关系和管理观察周期归集；经实质复核排除的组合从疑似金额中扣除。
+监控规则：滚动监测疑似组合金额及较上期变化，重点关注单一主体短期新增、多主体向同一关联受让方转让及确认后仍继续发生的交易。确认属于同一经济行为的，按合并口径重新履行程序。</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>指标名称：交易前审计评估备案程序完成率
-指标定义：反映应履行审计、评估及核准备案程序的产权交易，在确定底价或启动交易前完成全部适用程序的比例，用于评价交易定价基础和程序控制质量。
-指标计算：交易前审计评估备案程序完成率＝交易启动前已完成全部适用程序的事项数÷报告期应履行相关程序的产权交易事项总数×100%
-其中，是否应履行相关程序依据事项类型和制度规定判定；依法豁免且已取得有效依据的视为完成；报告期无适用事项时不计算比例。
-监控规则：按事项类型和责任单位定期分析完成率及未完成原因；任何未完成适用程序即启动交易的事项均应暂停后续实施，补充专业复核或重新履行程序后方可继续。</t>
+          <t>指标名称：审计评估备案程序未完成交易金额
+指标定义：反映应履行审计、评估或核准备案程序但在程序完整完成前已确定底价、挂牌或签约的产权交易规模。
+指标计算：程序未完成交易金额＝报告期内交易启动时适用审计评估备案程序尚未全部完成的产权交易实际对价合计
+其中，依法豁免且具有有效依据的事项不纳入；报告失效、备案与交易范围不匹配或程序倒序的事项纳入统计。
+监控规则：按月监测新增金额和未整改金额，并按应审未审、应评未评、未备案、报告失效或范围不匹配分类分析。出现新增时暂停后续交易，复核定价基础并补充履行程序。</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,11 +1026,11 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>指标名称：产权交易实际对价基准偏离率
-指标定义：反映交易实际取得的经济利益相对经批准定价基准的向下偏离程度，用于评价定价公允性及国有权益让渡风险。
-指标计算：产权交易实际对价基准偏离率＝（经批准定价基准－调整后实际对价）÷经批准定价基准×100%
-其中，调整后实际对价为成交价扣减债权豁免、费用代担、收益让渡等由转让方承担的经济利益；指标按单项交易计算，正值表示实际对价低于基准，经批准定价基准为零时不计算。
-监控规则：逐项监测向下偏离及其形成原因，区分公开竞价结果、经批准价格调整和未经批准权益让渡；未经充分论证和有效批准的向下偏离，应暂停签约或交割并重新审查定价及附带安排。</t>
+          <t>指标名称：产权交易对价向下偏离金额
+指标定义：反映调整后实际对价低于经批准定价基准的金额差额，用于监测产权交易定价不公允可能造成的国有权益损失规模。
+指标计算：产权交易对价向下偏离金额＝ΣMAX（经批准定价基准－调整后实际对价，0）
+其中，调整后实际对价为成交价扣减债权豁免、费用代担、收益让渡等由转让方承担的经济利益；经充分论证并取得有效批准的价格调整单独列示。
+监控规则：逐项监测向下偏离金额及其变化，重点关注偏离金额扩大、附带安排新增和批准依据不足的交易。未经有效批准的偏离应暂停签约或交割，重新审查定价及权益保障措施。</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1132,11 +1132,11 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>指标名称：进场及信息披露程序合规率
-指标定义：反映应公开交易事项完整履行进场、信息披露和条件变更程序的比例，用于评价产权交易公开、公平和可追溯程度。
-指标计算：进场及信息披露程序合规率＝完整履行适用进场及披露程序的事项数÷报告期应进场交易事项总数×100%
-其中，完整履行是指具有有效交易机构记录，披露期间符合规定，关键内容完整，挂牌条件变更已履行相应审批和披露程序；依法协议转让且批准依据有效的事项不纳入分母。
-监控规则：按交易类型和所属单位分析合规率及缺陷类型；未进场、披露不完整或擅自改变交易条件的事项不得继续签约交割，应重新进场、补充披露或履行变更程序。</t>
+          <t>指标名称：未规范进场及披露交易金额
+指标定义：反映应公开进场但无有效交易机构记录，或信息披露期间、内容、条件变更程序存在实质缺陷的产权交易规模。
+指标计算：未规范进场及披露交易金额＝相关程序缺陷尚未纠正的产权交易实际对价合计
+其中，依法采用非公开协议方式且批准依据有效的事项不纳入；同一交易存在多类缺陷时金额不重复计算。
+监控规则：按月监测新增金额、存量未整改金额和涉及法人主体，关注场外交易、披露实质缺失及擅自变更交易条件。发现风险后暂停签约交割，重新进场、补充披露或履行变更程序。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1224,11 +1224,11 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>指标名称：产权关键数据一致率
-指标定义：反映产权登记、工商登记、财务并表范围和实际持股台账中法人关键产权信息保持一致的程度，用于评价产权底数质量和并表管理准确性。
-指标计算：产权关键数据一致率＝关键字段全部一致或差异已由有效在途事项解释的企业数÷纳入多源比对的企业总数×100%
-其中，关键字段包括企业状态、股东名称、持股比例、控制关系、产权级次和并表状态；同一企业任一关键字段存在未解释差异即视为不一致。
-监控规则：定期分析总体一致率、差异类型和差异存续时间；对无法由在途事项解释或长期未消除的差异，明确责任数据源并核实真实产权关系，完成登记、工商或财务数据更正后闭环。</t>
+          <t>指标名称：产权多源信息差异法人户数
+指标定义：反映产权登记、工商登记、财务并表范围和实际持股台账之间存在关键字段差异的法人户数，用于监测产权底数失真及并表范围错漏风险。
+指标计算：产权多源信息差异法人户数＝期末存在未解释关键字段差异的法人主体去重户数
+其中，关键字段包括企业状态、股东名称、持股比例、控制关系、产权级次和并表状态；已关联有效在途变更且未超过计划完成日期的暂时差异单独列示。
+监控规则：按月监测差异法人户数的新增、消除和账龄变化，重点关注新增差异、长期未消除差异及影响控制关系或并表判断的差异，查明真实产权关系后更正责任数据源。</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1309,11 +1309,11 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>指标名称：控股企业关键治理权落实率
-指标定义：反映国有控股企业按照批准方案和章程落实董事席位、关键人员任免、重大事项表决及财务管控等控制权安排的程度，用于评价名义控股向实际控制转化的质量。
-指标计算：控股企业关键治理权落实率＝已实际落实的关键治理权项目数÷应落实的关键治理权项目总数×100%
-其中，应落实项目依据投资方案、章程和公司治理要求确定；仅有条款约定但未完成派员、授权或实际执行的，不计入已落实项目。
-监控规则：按控股企业定期评价落实率，并重点核查关键治理权缺失、长期空缺或无法实际行使的原因；影响实际控制的，应制定章程修订、人员调整、股权优化或退出方案。</t>
+          <t>指标名称：控股不控权企业国有权益账面价值
+指标定义：反映已确认或高度疑似控股不控权企业所对应的国有长期股权投资账面价值，用于监测实际控制权缺失所影响的国有资本规模。
+指标计算：控股不控权企业国有权益账面价值＝期末已确认或高度疑似控股不控权企业长期股权投资账面价值合计
+其中，控股不控权依据持股关系、董事席位、关键人员任免、重大事项表决、财务和印章管控等证据综合判断；已完成治理整改并经复核恢复控制的予以扣除。
+监控规则：按季度监测涉及企业户数、国有权益账面价值及较上期变化，重点关注新增企业、权益规模上升和长期未整改事项。根据控制缺失原因采取章程修订、人员调整、股权优化或退出措施。</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1395,11 +1395,11 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>指标名称：超层级及复杂嵌套企业占比
-指标定义：反映超过公司产权层级管理要求或存在无充分商业必要性复杂嵌套的企业占纳入监测企业的比重，用于评价产权架构精简程度和管理链条复杂性。
-指标计算：超层级及复杂嵌套企业占比＝经核实超出层级要求或存在复杂嵌套的企业数÷纳入产权层级监测的企业总数×100%
-其中，产权层级从集团总部沿控制链条计算；依法设立且具有充分商业必要性并取得专项批准的特殊架构单独列示，不作为未整改异常纳入分子。
-监控规则：定期分析占比变化、新增异常架构和存量压降进展；新增架构应在实施前论证必要性，存量异常逐户制定压缩或规范计划并跟踪完成质量。</t>
+          <t>指标名称：超层级及复杂嵌套法人户数
+指标定义：反映超过公司产权层级管理要求，或存在循环持股、重复中间载体等无充分商业必要性复杂架构的法人户数。
+指标计算：超层级及复杂嵌套法人户数＝期末经核实超出层级要求或存在复杂嵌套的法人主体去重户数
+其中，产权层级从集团总部沿控制链条计算；具有充分商业必要性并取得专项批准的特殊架构单独列示，整改完成并复核后从风险户数中扣除。
+监控规则：按季度监测风险法人户数、新增户数、压降户数和最长持股链条变化。新增复杂架构应及时核查必要性，存量风险逐户制定压缩或规范方案。</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1514,11 +1514,11 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>指标名称：专项审批前置完成率
-指标定义：反映无偿划转及境外产权处置事项在签署生效协议或移交控制权前完成全部适用专项审批和前置条件的比例，用于评价低频重大事项的程序质量。
-指标计算：专项审批前置完成率＝实施前已完成全部专项审批及前置条件的事项数÷报告期无偿划转及境外产权处置事项总数×100%
-其中，专项审批和前置条件依据事项类型、境内外适用规定及批复要求确定；事项方案发生实质变化后未经重新确认的，不视为完整完成。
-监控规则：按事项逐笔监测并在年度汇总分析完成质量；程序未完成或实施要素与批复不一致的，应停止后续实施，补充审批或调整方案并经专项复核。</t>
+          <t>指标名称：无有效专项批复处置资产金额
+指标定义：反映无偿划转或境外产权处置在缺少有效专项批复、批复失效或实际实施要素与批复不一致情况下涉及的资产或产权金额。
+指标计算：无有效专项批复处置资产金额＝相关程序风险尚未消除事项的处置标的评估值或账面价值合计
+其中，同一事项优先采用经核准或备案评估值，无评估值时采用最近一期账面价值；实施要素包括主体、标的、比例、方式和批复前置条件。
+监控规则：按事项监测新增风险金额和未整改金额，重大变化时开展专项复核。缺少批复或实施要素不一致的，应停止后续处置，补充审批或调整方案。</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>指标名称：评估范围未覆盖资产金额占比
-指标定义：反映评估申报范围未覆盖且无法合理解释的资产账面金额占基准日应评资产金额的比重，用于评价资产清查和评估范围完整性。
-指标计算：评估范围未覆盖资产金额占比＝经核实未纳入评估范围的应评资产账面金额÷评估基准日应纳入评估范围资产账面金额×100%
-其中，应评资产包括与交易标的相关的账内外资产及可辨认无形资产；已依法排除并形成书面依据的资产不计入分子，无法可靠取得账面金额的项目单独列示。
-监控规则：按评估事项开展范围勾稽，重点关注未覆盖金额、资产类别及形成原因；确认漏评的暂停备案和定价，补充清查评估并复核范围完整性。</t>
+          <t>指标名称：未纳入评估范围资产金额
+指标定义：反映经财务账、资产台账、权属资料与评估申报范围勾稽后，发现应评但未纳入评估范围的资产规模。
+指标计算：未纳入评估范围资产金额＝经核实遗漏的应评资产账面金额合计
+其中，包括与交易标的相关的账内外资产和可辨认无形资产；无法可靠取得账面金额的资产按类别及数量单独列示，不与金额合计混算。
+监控规则：按评估事项监测漏评金额、资产类别和较初始申报的变化，出现重大遗漏或新增漏评线索时暂停备案定价，补充清查评估并核查遗漏原因。</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>指标名称：交割后权属变更按期完成率
-指标定义：反映产权交易交割后，各项工商、产权登记及专项资产权属变更在批准计划期限内完成的比例，用于评价交割闭环和权利固化质量。
-指标计算：交割后权属变更按期完成率＝在计划期限内完成全部应办权属变更的事项数÷报告期应办理权属变更的已交割事项总数×100%
-其中，应办权属类型和计划期限依据批准的交割清单确定；因外部法定程序调整且已获批准变更计划的，按调整后计划评价。
-监控规则：按事项跟踪完成率和未办结原因，重点关注长期未完成及可能导致权利悬空的事项；责任单位应提出障碍解决、权益保全和更新计划，全部权属核验一致后办结。</t>
+          <t>指标名称：权属变更逾期交易金额
+指标定义：反映产权交易交割后，工商、产权登记或专项资产权属变更超过批准计划仍未完成所涉及的交易规模。
+指标计算：权属变更逾期交易金额＝期末至少一项应办权属变更逾期未完成事项的实际对价合计
+其中，应办权属类型和计划日期依据批准的交割清单确定；经批准调整计划的按调整后日期判断，同一交易金额不重复计算。
+监控规则：按月监测逾期金额、新增逾期金额和存续时间，重点关注权利悬空、受让方不配合或存在司法限制的事项，及时采取权益保全、追偿或暂停剩余交割措施。</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,11 +1817,11 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>指标名称：产权登记按期完成率
-指标定义：反映占有、变动和注销登记在适用规定期限内办结的比例，用于评价产权登记及时性和产权底数更新效率。
-指标计算：产权登记按期完成率＝在规定期限内办结的产权登记事项数÷报告期应办结产权登记事项总数×100%
-其中，办理期限依据经济行为完成日、登记类型及适用规定计算；退回补正不自动中止期限，确有外部原因且已履行延期审批的按批准计划评价。
-监控规则：按登记类型、责任单位和办理环节分析完成率及延误原因；对未按期办结事项逐项补正，核验登记结果与经济行为、工商信息一致后关闭。</t>
+          <t>指标名称：产权登记逾期法人户数
+指标定义：反映占有、变动或注销登记触发条件已经成立但超过适用期限仍未办结的法人户数，用于监测产权底数更新滞后风险。
+指标计算：产权登记逾期法人户数＝期末至少存在一项产权登记逾期未办结的法人主体去重户数
+其中，办理期限依据经济行为完成日、登记类型及适用规定确定；同一法人存在多项逾期登记按一户统计并保留事项明细。
+监控规则：按月监测新增逾期户数、办结户数和逾期账龄，重点关注长期未登记及工商已变更但产权登记未同步的法人，逐项补正并核验登记结果。</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1904,11 +1904,11 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>指标名称：退出清理按期完成率
-指标定义：反映退出企业按照批准方案及时完成字号、标识、无形资产、域名账号和证照清理的比例，用于评价退出风险隔离和品牌权益保护效果。
-指标计算：退出清理按期完成率＝计划期限内完成全部清理项目的退出企业数÷报告期应完成清理的退出企业总数×100%
-其中，应清理项目和计划期限以退出方案及交易协议为准；完成状态须有名称变更、许可终止、移交销毁等有效证明，部分完成不计入分子。
-监控规则：按退出企业跟踪完成率、未清理项目和存续时间；仍对外使用集团身份或无形资产的应优先处置，必要时采取合同追责和法律措施，全部复核通过后办结。</t>
+          <t>指标名称：退出清理未完成企业户数
+指标定义：反映企业退出后仍未完成字号、标识、商标许可、域名账号、印章证照等清理任务的企业户数。
+指标计算：退出清理未完成企业户数＝期末至少一项退出清理任务超过计划日期仍未办结的企业去重户数
+其中，应清理项目和计划日期以批准的退出方案及交易协议为准；部分完成仍计入风险户数，全部取得有效办结证明后扣除。
+监控规则：按月监测新增户数、清理完成户数和存续时间，重点关注仍对外使用集团身份、可能造成公众误认或品牌侵权的企业，必要时采取合同追责和法律措施。</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>指标名称：资质使用主体一致率
-指标定义：反映使用企业资质的项目中，合同签约、项目实施、关键人员、资源投入和财务核算主体与资质持有主体保持一致的比例，用于评价资质实质管控能力。
-指标计算：资质使用主体一致率＝经核验主体一致或具有合规内部协同依据的项目数÷报告期使用相关资质的项目总数×100%
-其中，合规内部协同须具备有效协议、审批依据且资质持有企业实际承担项目管理和法律责任；仅名义签约或收取管理费不视为一致。
-监控规则：按资质类型和项目定期抽查一致率，重点核查人员、资金和资源投入分离的项目；确认违规出借或变相使用的，应立即停止、收回授权并处置合同和现场风险。</t>
+          <t>指标名称：疑似违规使用资质项目合同金额
+指标定义：反映合同、项目实施、关键人员、资源投入或资金结算主体与资质持有主体分离，可能存在资质出借或变相使用的项目规模。
+指标计算：疑似违规使用资质项目合同金额＝命中资质使用主体异常条件且尚未排除的项目合同含税金额合计
+其中，具有有效内部协同协议且资质持有企业实际承担管理和法律责任的项目，经复核后从疑似金额中扣除。
+监控规则：按月监测疑似合同金额、新增项目和集中发生主体，重点关注人员、资金和项目管理多项分离的情形。确认违规后立即停止资质使用，处置合同、现场和法律责任风险。</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2078,15 +2078,18 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>不涉及持续KRI。
-专项清查关注：无有效授权使用集团字号、品牌或国有股东标识的企业名单，授权到期或退出后仍在使用的企业名单，以及使用范围与授权不一致事项。相关结果用于问题整改和管理评价，不作为日常自动预警指标。</t>
+          <t>指标名称：违规使用国有字号或标识企业户数
+指标定义：反映专项清查中发现无有效授权、超授权范围或退出后仍使用集团字号、品牌及国有股东标识的企业户数。
+指标计算：违规使用国有字号或标识企业户数＝本期专项清查确认存在违规使用情形的企业去重户数
+其中，同一企业存在多种违规使用情形按一户统计；已停止使用并完成名称、载体或授权整改且经复核通过的，从未整改存量中扣除。
+监控规则：结合年度或专项清查监测新增户数、未整改存量和问题持续时间；发现公众误认、融资增信或退出企业继续使用的，优先采取停止使用、名称变更和法律追索措施。</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>系统建立字号、品牌和国有股东标识授权台账，记录授权主体、载体、范围、期限、审批文件和退出条件，并在到期及产权关系变化时生成复核任务。
 专项清查阶段，系统汇集工商名称、产权关系、网站公众号及各单位自查信息，与授权台账进行比对，形成疑似无授权或超范围使用清单。
-疑似线索由品牌、法律和产权部门人工核实，整改通知、名称变更、标识撤除和法律处置结果留痕；不设置持续KRI自动定性。</t>
+疑似线索由品牌、法律和产权部门人工核实，专项清查结果按企业去重汇总违规使用户数；整改通知、名称变更、标识撤除和法律处置结果留痕，系统不自动作违规定性。</t>
         </is>
       </c>
     </row>
@@ -2164,8 +2167,11 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>不涉及持续KRI。
-专项清查关注：股东名册与实际出资人不一致、投资收益流向非登记股东、存在固定收益或回购兜底条款、项目实际经营主体与合同主体分离、仅按比例收取管理费等疑似线索。线索须经多部门核查后定性。</t>
+          <t>指标名称：代持挂靠等疑似风险企业户数
+指标定义：反映通过股东身份、出资资金、收益流向、治理安排、合同主体和实际经营关系交叉核验后，存在代持、虚假合资、挂靠经营或名股实债疑似特征的企业户数。
+指标计算：代持挂靠等疑似风险企业户数＝本期专项清查中至少命中一类疑似特征且尚未排除的企业去重户数
+其中，疑似特征包括登记股东与实际出资收益归属不一致、固定回报或回购兜底、合同主体与实际经营主体分离、仅收取管理费等；最终定性须经多部门联合核查。
+监控规则：按专项清查周期监测新增疑似户数、确认问题户数、排除户数和未整改存量。疑似户数上升或同一控制链条集中出现时扩大核查范围，确认问题后还原产权、终止安排或依法退出。</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2245,15 +2251,18 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>不涉及持续KRI。
-事项监测关注：合作方约定出资节点到期后的未实缴金额、未完成权属转移的非货币出资，以及实缴后短期异常转出的线索。按合资协议约定的出资节点形成清查名单，是否违约应依据有效协议、到账及权属凭证和经批准的调整安排核实。</t>
+          <t>指标名称：合作方逾期未到位出资金额
+指标定义：反映合作方超过章程或协议约定出资节点仍未实缴到位，以及非货币出资未完成权属转移的金额规模。
+指标计算：合作方逾期未到位出资金额＝到期应实缴金额－已核实实缴金额
+其中，已核实实缴金额以银行到账、验资或非货币资产权属转移凭证为准；经批准调整出资计划的按调整后节点计算，结果小于零时按零计。
+监控规则：按出资节点和季度监测新增逾期金额、未化解存量及合作方集中度。出现逾期时暂停我方后续对等出资和新增资源投入，启动催缴、违约追偿、股权调整或退出评估。</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>系统建立股东级出资计划，记录认缴金额、出资方式、计划节点、批准调整和违约条款，并关联银行流水、验资资料及非货币资产权属数据。
 节点到期后自动核验实缴状态并生成事项提醒；非货币出资进入人工核验任务，批准延期事项按新计划继续跟踪。
-专项清查视图展示未实缴、权属未转移和异常资金回流线索，催缴、暂停出资、股权调整或退出等处置结果回写风险台账；不设置持续KRI预警。</t>
+专项清查视图展示未实缴、权属未转移和异常资金回流线索，按有效出资节点计算逾期未到位金额并展示新增及存量变化；催缴、暂停出资、股权调整或退出等处置结果回写风险台账。</t>
         </is>
       </c>
     </row>
